--- a/data/trans_bre/IP1019-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP1019-Estudios-trans_bre.xlsx
@@ -714,7 +714,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,99</t>
+          <t>0,0; 0,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 0,0</t>
+          <t>-2,39; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 0,33</t>
+          <t>-0,19; 0,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
